--- a/SALTO_GYMNASTICS_2026-03-01_Girls_results.xlsx
+++ b/SALTO_GYMNASTICS_2026-03-01_Girls_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mandbt-my.sharepoint.com/personal/cat_mandbt_onmicrosoft_com/Documents/NGL/1ST MARCH/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{31731859-09B4-4B55-88BD-C3CB349B2519}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{31731859-09B4-4B55-88BD-C3CB349B2519}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{71BD45CB-DDCB-4CC3-BABC-44129B8ECAE2}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28905" yWindow="5445" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Vault" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1784" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1759" uniqueCount="125">
   <si>
     <t>Member ID</t>
   </si>
@@ -305,9 +305,6 @@
   </si>
   <si>
     <t>3229018</t>
-  </si>
-  <si>
-    <t>32</t>
   </si>
   <si>
     <t>2622516</t>
@@ -778,7 +775,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I49"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="36.83203125" customWidth="1"/>
@@ -790,7 +787,7 @@
     <col min="9" max="9" width="8.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -819,7 +816,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -839,7 +836,7 @@
         <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H2" t="s">
         <v>16</v>
@@ -848,7 +845,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -868,7 +865,7 @@
         <v>14</v>
       </c>
       <c r="G3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H3" t="s">
         <v>16</v>
@@ -877,7 +874,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -897,7 +894,7 @@
         <v>14</v>
       </c>
       <c r="G4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H4" t="s">
         <v>16</v>
@@ -906,7 +903,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -926,7 +923,7 @@
         <v>14</v>
       </c>
       <c r="G5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H5" t="s">
         <v>16</v>
@@ -935,7 +932,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -955,7 +952,7 @@
         <v>14</v>
       </c>
       <c r="G6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H6" t="s">
         <v>16</v>
@@ -964,7 +961,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -984,7 +981,7 @@
         <v>14</v>
       </c>
       <c r="G7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H7" t="s">
         <v>16</v>
@@ -993,7 +990,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -1013,7 +1010,7 @@
         <v>14</v>
       </c>
       <c r="G8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H8" t="s">
         <v>16</v>
@@ -1022,7 +1019,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -1042,7 +1039,7 @@
         <v>14</v>
       </c>
       <c r="G9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H9" t="s">
         <v>16</v>
@@ -1051,7 +1048,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -1071,7 +1068,7 @@
         <v>14</v>
       </c>
       <c r="G10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H10" t="s">
         <v>16</v>
@@ -1080,7 +1077,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>32</v>
       </c>
@@ -1100,7 +1097,7 @@
         <v>14</v>
       </c>
       <c r="G11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H11" t="s">
         <v>16</v>
@@ -1109,7 +1106,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -1129,7 +1126,7 @@
         <v>14</v>
       </c>
       <c r="G12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H12" t="s">
         <v>16</v>
@@ -1138,7 +1135,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>37</v>
       </c>
@@ -1158,7 +1155,7 @@
         <v>14</v>
       </c>
       <c r="G13" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H13" t="s">
         <v>16</v>
@@ -1167,7 +1164,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>39</v>
       </c>
@@ -1187,7 +1184,7 @@
         <v>14</v>
       </c>
       <c r="G14" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H14" t="s">
         <v>16</v>
@@ -1196,7 +1193,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>41</v>
       </c>
@@ -1216,7 +1213,7 @@
         <v>14</v>
       </c>
       <c r="G15" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H15" t="s">
         <v>16</v>
@@ -1225,7 +1222,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>42</v>
       </c>
@@ -1245,7 +1242,7 @@
         <v>14</v>
       </c>
       <c r="G16" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H16" t="s">
         <v>16</v>
@@ -1254,7 +1251,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>44</v>
       </c>
@@ -1274,7 +1271,7 @@
         <v>14</v>
       </c>
       <c r="G17" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H17" t="s">
         <v>16</v>
@@ -1283,7 +1280,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>47</v>
       </c>
@@ -1303,7 +1300,7 @@
         <v>14</v>
       </c>
       <c r="G18" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H18" t="s">
         <v>16</v>
@@ -1312,7 +1309,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>49</v>
       </c>
@@ -1332,7 +1329,7 @@
         <v>14</v>
       </c>
       <c r="G19" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H19" t="s">
         <v>16</v>
@@ -1341,7 +1338,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>50</v>
       </c>
@@ -1361,7 +1358,7 @@
         <v>14</v>
       </c>
       <c r="G20" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H20" t="s">
         <v>16</v>
@@ -1370,7 +1367,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>52</v>
       </c>
@@ -1390,7 +1387,7 @@
         <v>14</v>
       </c>
       <c r="G21" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H21" t="s">
         <v>16</v>
@@ -1399,7 +1396,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>54</v>
       </c>
@@ -1419,7 +1416,7 @@
         <v>14</v>
       </c>
       <c r="G22" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H22" t="s">
         <v>16</v>
@@ -1428,7 +1425,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>56</v>
       </c>
@@ -1448,7 +1445,7 @@
         <v>14</v>
       </c>
       <c r="G23" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H23" t="s">
         <v>16</v>
@@ -1457,7 +1454,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>58</v>
       </c>
@@ -1477,7 +1474,7 @@
         <v>14</v>
       </c>
       <c r="G24" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H24" t="s">
         <v>16</v>
@@ -1486,7 +1483,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>60</v>
       </c>
@@ -1506,7 +1503,7 @@
         <v>14</v>
       </c>
       <c r="G25" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H25" t="s">
         <v>16</v>
@@ -1515,7 +1512,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>61</v>
       </c>
@@ -1535,7 +1532,7 @@
         <v>14</v>
       </c>
       <c r="G26" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H26" t="s">
         <v>16</v>
@@ -1544,7 +1541,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>63</v>
       </c>
@@ -1564,7 +1561,7 @@
         <v>14</v>
       </c>
       <c r="G27" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H27" t="s">
         <v>16</v>
@@ -1573,7 +1570,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>65</v>
       </c>
@@ -1593,7 +1590,7 @@
         <v>14</v>
       </c>
       <c r="G28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H28" t="s">
         <v>16</v>
@@ -1602,7 +1599,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>67</v>
       </c>
@@ -1622,7 +1619,7 @@
         <v>14</v>
       </c>
       <c r="G29" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H29" t="s">
         <v>16</v>
@@ -1631,7 +1628,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>70</v>
       </c>
@@ -1651,7 +1648,7 @@
         <v>14</v>
       </c>
       <c r="G30" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H30" t="s">
         <v>16</v>
@@ -1660,7 +1657,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>72</v>
       </c>
@@ -1680,7 +1677,7 @@
         <v>14</v>
       </c>
       <c r="G31" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H31" t="s">
         <v>16</v>
@@ -1689,7 +1686,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>74</v>
       </c>
@@ -1709,7 +1706,7 @@
         <v>14</v>
       </c>
       <c r="G32" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H32" t="s">
         <v>16</v>
@@ -1718,7 +1715,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>75</v>
       </c>
@@ -1738,7 +1735,7 @@
         <v>14</v>
       </c>
       <c r="G33" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H33" t="s">
         <v>16</v>
@@ -1747,7 +1744,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>77</v>
       </c>
@@ -1767,7 +1764,7 @@
         <v>14</v>
       </c>
       <c r="G34" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H34" t="s">
         <v>16</v>
@@ -1776,7 +1773,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>79</v>
       </c>
@@ -1796,7 +1793,7 @@
         <v>14</v>
       </c>
       <c r="G35" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H35" t="s">
         <v>16</v>
@@ -1805,7 +1802,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>80</v>
       </c>
@@ -1825,7 +1822,7 @@
         <v>14</v>
       </c>
       <c r="G36" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H36" t="s">
         <v>16</v>
@@ -1834,7 +1831,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>81</v>
       </c>
@@ -1854,7 +1851,7 @@
         <v>14</v>
       </c>
       <c r="G37" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H37" t="s">
         <v>16</v>
@@ -1863,7 +1860,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>82</v>
       </c>
@@ -1883,7 +1880,7 @@
         <v>14</v>
       </c>
       <c r="G38" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H38" t="s">
         <v>84</v>
@@ -1892,7 +1889,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>85</v>
       </c>
@@ -1912,7 +1909,7 @@
         <v>14</v>
       </c>
       <c r="G39" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H39" t="s">
         <v>84</v>
@@ -1921,7 +1918,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>86</v>
       </c>
@@ -1941,7 +1938,7 @@
         <v>14</v>
       </c>
       <c r="G40" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H40" t="s">
         <v>84</v>
@@ -1950,7 +1947,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>87</v>
       </c>
@@ -1970,7 +1967,7 @@
         <v>14</v>
       </c>
       <c r="G41" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H41" t="s">
         <v>84</v>
@@ -1979,7 +1976,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>88</v>
       </c>
@@ -1999,7 +1996,7 @@
         <v>14</v>
       </c>
       <c r="G42" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H42" t="s">
         <v>84</v>
@@ -2008,7 +2005,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>89</v>
       </c>
@@ -2028,7 +2025,7 @@
         <v>14</v>
       </c>
       <c r="G43" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H43" t="s">
         <v>84</v>
@@ -2037,7 +2034,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>90</v>
       </c>
@@ -2057,7 +2054,7 @@
         <v>14</v>
       </c>
       <c r="G44" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H44" t="s">
         <v>84</v>
@@ -2066,7 +2063,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>91</v>
       </c>
@@ -2086,7 +2083,7 @@
         <v>14</v>
       </c>
       <c r="G45" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H45" t="s">
         <v>84</v>
@@ -2095,7 +2092,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>92</v>
       </c>
@@ -2115,7 +2112,7 @@
         <v>14</v>
       </c>
       <c r="G46" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H46" t="s">
         <v>84</v>
@@ -2124,7 +2121,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>93</v>
       </c>
@@ -2144,7 +2141,7 @@
         <v>14</v>
       </c>
       <c r="G47" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H47" t="s">
         <v>84</v>
@@ -2153,9 +2150,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
-        <v>94</v>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A48">
+        <v>4600880</v>
       </c>
       <c r="B48" t="s">
         <v>34</v>
@@ -2173,7 +2170,7 @@
         <v>14</v>
       </c>
       <c r="G48" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H48" t="s">
         <v>84</v>
@@ -2182,9 +2179,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B49" t="s">
         <v>34</v>
@@ -2202,7 +2199,7 @@
         <v>14</v>
       </c>
       <c r="G49" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H49" t="s">
         <v>84</v>
@@ -2214,7 +2211,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:I1 A3:F49 A2:F2 H2:I2 H3:I49" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:I1 A3:F47 A2:F2 H2:I2 H3:I49 A49:F49 B48:F48" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2222,7 +2219,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I49"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="36.83203125" customWidth="1"/>
@@ -2234,7 +2231,7 @@
     <col min="9" max="9" width="8.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2263,7 +2260,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>20</v>
       </c>
@@ -2283,7 +2280,7 @@
         <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H2" t="s">
         <v>16</v>
@@ -2292,7 +2289,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -2306,13 +2303,13 @@
         <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F3" t="s">
         <v>14</v>
       </c>
       <c r="G3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H3" t="s">
         <v>16</v>
@@ -2321,7 +2318,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -2341,7 +2338,7 @@
         <v>14</v>
       </c>
       <c r="G4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H4" t="s">
         <v>16</v>
@@ -2350,7 +2347,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -2364,13 +2361,13 @@
         <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F5" t="s">
         <v>14</v>
       </c>
       <c r="G5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H5" t="s">
         <v>16</v>
@@ -2379,7 +2376,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -2399,7 +2396,7 @@
         <v>14</v>
       </c>
       <c r="G6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H6" t="s">
         <v>16</v>
@@ -2408,7 +2405,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -2428,7 +2425,7 @@
         <v>14</v>
       </c>
       <c r="G7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H7" t="s">
         <v>16</v>
@@ -2437,7 +2434,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -2457,7 +2454,7 @@
         <v>14</v>
       </c>
       <c r="G8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H8" t="s">
         <v>16</v>
@@ -2466,7 +2463,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -2486,7 +2483,7 @@
         <v>14</v>
       </c>
       <c r="G9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H9" t="s">
         <v>16</v>
@@ -2495,7 +2492,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -2515,7 +2512,7 @@
         <v>14</v>
       </c>
       <c r="G10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H10" t="s">
         <v>16</v>
@@ -2524,7 +2521,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>32</v>
       </c>
@@ -2544,7 +2541,7 @@
         <v>14</v>
       </c>
       <c r="G11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H11" t="s">
         <v>16</v>
@@ -2553,7 +2550,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -2567,13 +2564,13 @@
         <v>35</v>
       </c>
       <c r="E12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F12" t="s">
         <v>14</v>
       </c>
       <c r="G12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H12" t="s">
         <v>16</v>
@@ -2582,7 +2579,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>37</v>
       </c>
@@ -2596,13 +2593,13 @@
         <v>35</v>
       </c>
       <c r="E13" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F13" t="s">
         <v>14</v>
       </c>
       <c r="G13" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H13" t="s">
         <v>16</v>
@@ -2611,7 +2608,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>42</v>
       </c>
@@ -2631,7 +2628,7 @@
         <v>14</v>
       </c>
       <c r="G14" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H14" t="s">
         <v>16</v>
@@ -2640,7 +2637,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>50</v>
       </c>
@@ -2660,7 +2657,7 @@
         <v>14</v>
       </c>
       <c r="G15" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H15" t="s">
         <v>16</v>
@@ -2669,7 +2666,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>52</v>
       </c>
@@ -2683,13 +2680,13 @@
         <v>35</v>
       </c>
       <c r="E16" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F16" t="s">
         <v>14</v>
       </c>
       <c r="G16" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H16" t="s">
         <v>16</v>
@@ -2698,7 +2695,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>60</v>
       </c>
@@ -2712,13 +2709,13 @@
         <v>35</v>
       </c>
       <c r="E17" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F17" t="s">
         <v>14</v>
       </c>
       <c r="G17" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H17" t="s">
         <v>16</v>
@@ -2727,7 +2724,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>41</v>
       </c>
@@ -2747,7 +2744,7 @@
         <v>14</v>
       </c>
       <c r="G18" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H18" t="s">
         <v>16</v>
@@ -2756,7 +2753,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>47</v>
       </c>
@@ -2770,13 +2767,13 @@
         <v>35</v>
       </c>
       <c r="E19" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F19" t="s">
         <v>14</v>
       </c>
       <c r="G19" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H19" t="s">
         <v>16</v>
@@ -2785,7 +2782,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>54</v>
       </c>
@@ -2805,7 +2802,7 @@
         <v>14</v>
       </c>
       <c r="G20" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H20" t="s">
         <v>16</v>
@@ -2814,7 +2811,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>63</v>
       </c>
@@ -2834,7 +2831,7 @@
         <v>14</v>
       </c>
       <c r="G21" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H21" t="s">
         <v>16</v>
@@ -2843,7 +2840,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>61</v>
       </c>
@@ -2863,7 +2860,7 @@
         <v>14</v>
       </c>
       <c r="G22" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H22" t="s">
         <v>16</v>
@@ -2872,7 +2869,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>56</v>
       </c>
@@ -2886,13 +2883,13 @@
         <v>35</v>
       </c>
       <c r="E23" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F23" t="s">
         <v>14</v>
       </c>
       <c r="G23" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H23" t="s">
         <v>16</v>
@@ -2901,7 +2898,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>58</v>
       </c>
@@ -2921,7 +2918,7 @@
         <v>14</v>
       </c>
       <c r="G24" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H24" t="s">
         <v>16</v>
@@ -2930,7 +2927,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>44</v>
       </c>
@@ -2950,7 +2947,7 @@
         <v>14</v>
       </c>
       <c r="G25" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H25" t="s">
         <v>16</v>
@@ -2959,7 +2956,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>49</v>
       </c>
@@ -2973,13 +2970,13 @@
         <v>35</v>
       </c>
       <c r="E26" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F26" t="s">
         <v>14</v>
       </c>
       <c r="G26" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H26" t="s">
         <v>16</v>
@@ -2988,7 +2985,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>65</v>
       </c>
@@ -3008,7 +3005,7 @@
         <v>14</v>
       </c>
       <c r="G27" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H27" t="s">
         <v>16</v>
@@ -3017,7 +3014,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>39</v>
       </c>
@@ -3031,13 +3028,13 @@
         <v>35</v>
       </c>
       <c r="E28" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F28" t="s">
         <v>14</v>
       </c>
       <c r="G28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H28" t="s">
         <v>16</v>
@@ -3046,7 +3043,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>72</v>
       </c>
@@ -3066,7 +3063,7 @@
         <v>14</v>
       </c>
       <c r="G29" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H29" t="s">
         <v>16</v>
@@ -3075,7 +3072,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>67</v>
       </c>
@@ -3095,7 +3092,7 @@
         <v>14</v>
       </c>
       <c r="G30" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H30" t="s">
         <v>16</v>
@@ -3104,7 +3101,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>70</v>
       </c>
@@ -3124,7 +3121,7 @@
         <v>14</v>
       </c>
       <c r="G31" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H31" t="s">
         <v>16</v>
@@ -3133,7 +3130,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>74</v>
       </c>
@@ -3153,7 +3150,7 @@
         <v>14</v>
       </c>
       <c r="G32" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H32" t="s">
         <v>16</v>
@@ -3162,7 +3159,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>79</v>
       </c>
@@ -3182,7 +3179,7 @@
         <v>14</v>
       </c>
       <c r="G33" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H33" t="s">
         <v>16</v>
@@ -3191,7 +3188,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>75</v>
       </c>
@@ -3211,7 +3208,7 @@
         <v>14</v>
       </c>
       <c r="G34" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H34" t="s">
         <v>16</v>
@@ -3220,7 +3217,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>77</v>
       </c>
@@ -3234,13 +3231,13 @@
         <v>76</v>
       </c>
       <c r="E35" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F35" t="s">
         <v>14</v>
       </c>
       <c r="G35" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H35" t="s">
         <v>16</v>
@@ -3249,7 +3246,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>81</v>
       </c>
@@ -3269,7 +3266,7 @@
         <v>14</v>
       </c>
       <c r="G36" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H36" t="s">
         <v>16</v>
@@ -3278,7 +3275,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>80</v>
       </c>
@@ -3298,7 +3295,7 @@
         <v>14</v>
       </c>
       <c r="G37" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H37" t="s">
         <v>16</v>
@@ -3307,7 +3304,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>87</v>
       </c>
@@ -3321,13 +3318,13 @@
         <v>76</v>
       </c>
       <c r="E38" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F38" t="s">
         <v>14</v>
       </c>
       <c r="G38" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H38" t="s">
         <v>84</v>
@@ -3336,7 +3333,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>86</v>
       </c>
@@ -3356,7 +3353,7 @@
         <v>14</v>
       </c>
       <c r="G39" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H39" t="s">
         <v>84</v>
@@ -3365,7 +3362,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>85</v>
       </c>
@@ -3385,7 +3382,7 @@
         <v>14</v>
       </c>
       <c r="G40" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H40" t="s">
         <v>84</v>
@@ -3394,7 +3391,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>82</v>
       </c>
@@ -3408,13 +3405,13 @@
         <v>76</v>
       </c>
       <c r="E41" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F41" t="s">
         <v>14</v>
       </c>
       <c r="G41" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H41" t="s">
         <v>84</v>
@@ -3423,7 +3420,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>88</v>
       </c>
@@ -3443,7 +3440,7 @@
         <v>14</v>
       </c>
       <c r="G42" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H42" t="s">
         <v>84</v>
@@ -3452,7 +3449,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>89</v>
       </c>
@@ -3472,7 +3469,7 @@
         <v>14</v>
       </c>
       <c r="G43" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H43" t="s">
         <v>84</v>
@@ -3481,7 +3478,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>91</v>
       </c>
@@ -3501,7 +3498,7 @@
         <v>14</v>
       </c>
       <c r="G44" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H44" t="s">
         <v>84</v>
@@ -3510,7 +3507,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>90</v>
       </c>
@@ -3530,7 +3527,7 @@
         <v>14</v>
       </c>
       <c r="G45" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H45" t="s">
         <v>84</v>
@@ -3539,7 +3536,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>92</v>
       </c>
@@ -3559,7 +3556,7 @@
         <v>14</v>
       </c>
       <c r="G46" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H46" t="s">
         <v>84</v>
@@ -3568,9 +3565,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
-        <v>94</v>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A47">
+        <v>4600880</v>
       </c>
       <c r="B47" t="s">
         <v>34</v>
@@ -3588,7 +3585,7 @@
         <v>14</v>
       </c>
       <c r="G47" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H47" t="s">
         <v>84</v>
@@ -3597,7 +3594,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>93</v>
       </c>
@@ -3611,13 +3608,13 @@
         <v>35</v>
       </c>
       <c r="E48" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F48" t="s">
         <v>14</v>
       </c>
       <c r="G48" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H48" t="s">
         <v>84</v>
@@ -3626,9 +3623,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B49" t="s">
         <v>34</v>
@@ -3646,7 +3643,7 @@
         <v>14</v>
       </c>
       <c r="G49" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H49" t="s">
         <v>84</v>
@@ -3658,7 +3655,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:F49 H1:I49" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:F46 H1:I49 A48:F49 B47:F47" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3666,7 +3663,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:I49"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="36.83203125" customWidth="1"/>
@@ -3678,7 +3675,7 @@
     <col min="9" max="9" width="8.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3707,7 +3704,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -3721,13 +3718,13 @@
         <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F2" t="s">
         <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H2" t="s">
         <v>16</v>
@@ -3736,7 +3733,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>26</v>
       </c>
@@ -3756,7 +3753,7 @@
         <v>14</v>
       </c>
       <c r="G3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H3" t="s">
         <v>16</v>
@@ -3765,7 +3762,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -3785,7 +3782,7 @@
         <v>14</v>
       </c>
       <c r="G4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H4" t="s">
         <v>16</v>
@@ -3794,7 +3791,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -3808,13 +3805,13 @@
         <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F5" t="s">
         <v>14</v>
       </c>
       <c r="G5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H5" t="s">
         <v>16</v>
@@ -3823,7 +3820,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -3843,7 +3840,7 @@
         <v>14</v>
       </c>
       <c r="G6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H6" t="s">
         <v>16</v>
@@ -3852,7 +3849,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -3872,7 +3869,7 @@
         <v>14</v>
       </c>
       <c r="G7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H7" t="s">
         <v>16</v>
@@ -3881,7 +3878,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -3895,13 +3892,13 @@
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F8" t="s">
         <v>14</v>
       </c>
       <c r="G8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H8" t="s">
         <v>16</v>
@@ -3910,7 +3907,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -3930,7 +3927,7 @@
         <v>14</v>
       </c>
       <c r="G9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H9" t="s">
         <v>16</v>
@@ -3939,7 +3936,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -3959,7 +3956,7 @@
         <v>14</v>
       </c>
       <c r="G10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H10" t="s">
         <v>16</v>
@@ -3968,7 +3965,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>31</v>
       </c>
@@ -3988,7 +3985,7 @@
         <v>14</v>
       </c>
       <c r="G11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H11" t="s">
         <v>16</v>
@@ -3997,7 +3994,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -4017,7 +4014,7 @@
         <v>14</v>
       </c>
       <c r="G12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H12" t="s">
         <v>16</v>
@@ -4026,7 +4023,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>47</v>
       </c>
@@ -4046,7 +4043,7 @@
         <v>14</v>
       </c>
       <c r="G13" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H13" t="s">
         <v>16</v>
@@ -4055,7 +4052,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>37</v>
       </c>
@@ -4075,7 +4072,7 @@
         <v>14</v>
       </c>
       <c r="G14" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H14" t="s">
         <v>16</v>
@@ -4084,7 +4081,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>52</v>
       </c>
@@ -4104,7 +4101,7 @@
         <v>14</v>
       </c>
       <c r="G15" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H15" t="s">
         <v>16</v>
@@ -4113,7 +4110,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>49</v>
       </c>
@@ -4133,7 +4130,7 @@
         <v>14</v>
       </c>
       <c r="G16" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H16" t="s">
         <v>16</v>
@@ -4142,7 +4139,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>60</v>
       </c>
@@ -4162,7 +4159,7 @@
         <v>14</v>
       </c>
       <c r="G17" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H17" t="s">
         <v>16</v>
@@ -4171,7 +4168,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>44</v>
       </c>
@@ -4185,13 +4182,13 @@
         <v>35</v>
       </c>
       <c r="E18" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F18" t="s">
         <v>14</v>
       </c>
       <c r="G18" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H18" t="s">
         <v>16</v>
@@ -4200,7 +4197,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>42</v>
       </c>
@@ -4220,7 +4217,7 @@
         <v>14</v>
       </c>
       <c r="G19" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H19" t="s">
         <v>16</v>
@@ -4229,7 +4226,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>63</v>
       </c>
@@ -4249,7 +4246,7 @@
         <v>14</v>
       </c>
       <c r="G20" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H20" t="s">
         <v>16</v>
@@ -4258,7 +4255,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>65</v>
       </c>
@@ -4278,7 +4275,7 @@
         <v>14</v>
       </c>
       <c r="G21" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H21" t="s">
         <v>16</v>
@@ -4287,7 +4284,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>61</v>
       </c>
@@ -4307,7 +4304,7 @@
         <v>14</v>
       </c>
       <c r="G22" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H22" t="s">
         <v>16</v>
@@ -4316,7 +4313,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>50</v>
       </c>
@@ -4330,13 +4327,13 @@
         <v>35</v>
       </c>
       <c r="E23" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F23" t="s">
         <v>14</v>
       </c>
       <c r="G23" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H23" t="s">
         <v>16</v>
@@ -4345,7 +4342,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>39</v>
       </c>
@@ -4359,13 +4356,13 @@
         <v>35</v>
       </c>
       <c r="E24" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F24" t="s">
         <v>14</v>
       </c>
       <c r="G24" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H24" t="s">
         <v>16</v>
@@ -4374,7 +4371,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>58</v>
       </c>
@@ -4388,13 +4385,13 @@
         <v>35</v>
       </c>
       <c r="E25" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F25" t="s">
         <v>14</v>
       </c>
       <c r="G25" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H25" t="s">
         <v>16</v>
@@ -4403,7 +4400,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>41</v>
       </c>
@@ -4417,13 +4414,13 @@
         <v>35</v>
       </c>
       <c r="E26" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F26" t="s">
         <v>14</v>
       </c>
       <c r="G26" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H26" t="s">
         <v>16</v>
@@ -4432,7 +4429,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>54</v>
       </c>
@@ -4452,7 +4449,7 @@
         <v>14</v>
       </c>
       <c r="G27" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H27" t="s">
         <v>16</v>
@@ -4461,7 +4458,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>56</v>
       </c>
@@ -4475,13 +4472,13 @@
         <v>35</v>
       </c>
       <c r="E28" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F28" t="s">
         <v>14</v>
       </c>
       <c r="G28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H28" t="s">
         <v>16</v>
@@ -4490,7 +4487,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>67</v>
       </c>
@@ -4510,7 +4507,7 @@
         <v>14</v>
       </c>
       <c r="G29" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H29" t="s">
         <v>16</v>
@@ -4519,7 +4516,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>72</v>
       </c>
@@ -4533,13 +4530,13 @@
         <v>35</v>
       </c>
       <c r="E30" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F30" t="s">
         <v>14</v>
       </c>
       <c r="G30" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H30" t="s">
         <v>16</v>
@@ -4548,7 +4545,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>70</v>
       </c>
@@ -4568,7 +4565,7 @@
         <v>14</v>
       </c>
       <c r="G31" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H31" t="s">
         <v>16</v>
@@ -4577,7 +4574,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>74</v>
       </c>
@@ -4597,7 +4594,7 @@
         <v>14</v>
       </c>
       <c r="G32" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H32" t="s">
         <v>16</v>
@@ -4606,7 +4603,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>79</v>
       </c>
@@ -4620,13 +4617,13 @@
         <v>76</v>
       </c>
       <c r="E33" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F33" t="s">
         <v>14</v>
       </c>
       <c r="G33" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H33" t="s">
         <v>16</v>
@@ -4635,7 +4632,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>77</v>
       </c>
@@ -4655,7 +4652,7 @@
         <v>14</v>
       </c>
       <c r="G34" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H34" t="s">
         <v>16</v>
@@ -4664,7 +4661,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>75</v>
       </c>
@@ -4678,13 +4675,13 @@
         <v>76</v>
       </c>
       <c r="E35" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F35" t="s">
         <v>14</v>
       </c>
       <c r="G35" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H35" t="s">
         <v>16</v>
@@ -4693,7 +4690,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>80</v>
       </c>
@@ -4713,7 +4710,7 @@
         <v>14</v>
       </c>
       <c r="G36" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H36" t="s">
         <v>16</v>
@@ -4722,7 +4719,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>81</v>
       </c>
@@ -4736,13 +4733,13 @@
         <v>76</v>
       </c>
       <c r="E37" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F37" t="s">
         <v>14</v>
       </c>
       <c r="G37" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H37" t="s">
         <v>16</v>
@@ -4751,7 +4748,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>82</v>
       </c>
@@ -4771,7 +4768,7 @@
         <v>14</v>
       </c>
       <c r="G38" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H38" t="s">
         <v>84</v>
@@ -4780,7 +4777,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>86</v>
       </c>
@@ -4794,13 +4791,13 @@
         <v>76</v>
       </c>
       <c r="E39" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F39" t="s">
         <v>14</v>
       </c>
       <c r="G39" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H39" t="s">
         <v>84</v>
@@ -4809,7 +4806,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>87</v>
       </c>
@@ -4829,7 +4826,7 @@
         <v>14</v>
       </c>
       <c r="G40" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H40" t="s">
         <v>84</v>
@@ -4838,7 +4835,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>85</v>
       </c>
@@ -4852,13 +4849,13 @@
         <v>76</v>
       </c>
       <c r="E41" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F41" t="s">
         <v>14</v>
       </c>
       <c r="G41" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H41" t="s">
         <v>84</v>
@@ -4867,7 +4864,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>90</v>
       </c>
@@ -4881,13 +4878,13 @@
         <v>76</v>
       </c>
       <c r="E42" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F42" t="s">
         <v>14</v>
       </c>
       <c r="G42" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H42" t="s">
         <v>84</v>
@@ -4896,7 +4893,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>89</v>
       </c>
@@ -4910,13 +4907,13 @@
         <v>76</v>
       </c>
       <c r="E43" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F43" t="s">
         <v>14</v>
       </c>
       <c r="G43" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H43" t="s">
         <v>84</v>
@@ -4925,7 +4922,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>88</v>
       </c>
@@ -4945,7 +4942,7 @@
         <v>14</v>
       </c>
       <c r="G44" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H44" t="s">
         <v>84</v>
@@ -4954,7 +4951,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>91</v>
       </c>
@@ -4968,13 +4965,13 @@
         <v>76</v>
       </c>
       <c r="E45" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F45" t="s">
         <v>14</v>
       </c>
       <c r="G45" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H45" t="s">
         <v>84</v>
@@ -4983,9 +4980,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
-        <v>94</v>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <v>4600880</v>
       </c>
       <c r="B46" t="s">
         <v>34</v>
@@ -4997,13 +4994,13 @@
         <v>35</v>
       </c>
       <c r="E46" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F46" t="s">
         <v>14</v>
       </c>
       <c r="G46" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H46" t="s">
         <v>84</v>
@@ -5012,7 +5009,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>93</v>
       </c>
@@ -5032,7 +5029,7 @@
         <v>14</v>
       </c>
       <c r="G47" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H47" t="s">
         <v>84</v>
@@ -5041,7 +5038,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>92</v>
       </c>
@@ -5061,7 +5058,7 @@
         <v>14</v>
       </c>
       <c r="G48" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H48" t="s">
         <v>84</v>
@@ -5070,9 +5067,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B49" t="s">
         <v>34</v>
@@ -5090,7 +5087,7 @@
         <v>14</v>
       </c>
       <c r="G49" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H49" t="s">
         <v>84</v>
@@ -5102,7 +5099,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:F49 H1:I49" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:F45 H1:I49 A47:F49 B46:F46" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -5110,7 +5107,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:I49"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="36.83203125" customWidth="1"/>
@@ -5122,7 +5119,7 @@
     <col min="9" max="9" width="8.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5151,85 +5148,85 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>20</v>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>4600880</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="E2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="F2" t="s">
         <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H2" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="I2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>88</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>76</v>
       </c>
       <c r="E3" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="F3" t="s">
         <v>14</v>
       </c>
       <c r="G3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H3" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="I3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>80</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>76</v>
       </c>
       <c r="E4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F4" t="s">
         <v>14</v>
       </c>
       <c r="G4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H4" t="s">
         <v>16</v>
@@ -5238,122 +5235,125 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>94</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="E5" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="F5" t="s">
         <v>14</v>
       </c>
       <c r="G5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H5" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="I5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>81</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="D6" t="s">
-        <v>12</v>
+        <v>76</v>
       </c>
       <c r="E6" t="s">
+        <v>118</v>
+      </c>
+      <c r="F6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" t="s">
+        <v>124</v>
+      </c>
+      <c r="H6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>92</v>
+      </c>
+      <c r="B7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" t="s">
         <v>114</v>
       </c>
-      <c r="F6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" t="s">
-        <v>125</v>
-      </c>
-      <c r="H6" t="s">
-        <v>16</v>
-      </c>
-      <c r="I6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" t="s">
-        <v>115</v>
-      </c>
       <c r="F7" t="s">
         <v>14</v>
       </c>
       <c r="G7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H7" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="I7" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>27</v>
+        <v>89</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="C8" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="D8" t="s">
-        <v>12</v>
+        <v>76</v>
+      </c>
+      <c r="E8" t="s">
+        <v>117</v>
       </c>
       <c r="F8" t="s">
         <v>14</v>
       </c>
       <c r="G8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H8" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="I8" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="B9" t="s">
         <v>10</v>
@@ -5362,16 +5362,16 @@
         <v>30</v>
       </c>
       <c r="D9" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="E9" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="F9" t="s">
         <v>14</v>
       </c>
       <c r="G9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H9" t="s">
         <v>16</v>
@@ -5380,38 +5380,38 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>82</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="C10" t="s">
         <v>30</v>
       </c>
       <c r="D10" t="s">
-        <v>12</v>
+        <v>76</v>
       </c>
       <c r="E10" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="F10" t="s">
         <v>14</v>
       </c>
       <c r="G10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H10" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="I10" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B11" t="s">
         <v>10</v>
@@ -5423,13 +5423,13 @@
         <v>12</v>
       </c>
       <c r="E11" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="F11" t="s">
         <v>14</v>
       </c>
       <c r="G11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H11" t="s">
         <v>16</v>
@@ -5438,27 +5438,27 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="B12" t="s">
         <v>34</v>
       </c>
       <c r="C12" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="D12" t="s">
         <v>35</v>
       </c>
       <c r="E12" t="s">
-        <v>40</v>
+        <v>109</v>
       </c>
       <c r="F12" t="s">
         <v>14</v>
       </c>
       <c r="G12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H12" t="s">
         <v>16</v>
@@ -5467,9 +5467,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B13" t="s">
         <v>34</v>
@@ -5487,7 +5487,7 @@
         <v>14</v>
       </c>
       <c r="G13" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H13" t="s">
         <v>16</v>
@@ -5496,41 +5496,41 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>39</v>
+        <v>90</v>
       </c>
       <c r="B14" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="C14" t="s">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="D14" t="s">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="E14" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F14" t="s">
         <v>14</v>
       </c>
       <c r="G14" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H14" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="I14" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C15" t="s">
         <v>30</v>
@@ -5539,13 +5539,13 @@
         <v>35</v>
       </c>
       <c r="E15" t="s">
-        <v>118</v>
+        <v>40</v>
       </c>
       <c r="F15" t="s">
         <v>14</v>
       </c>
       <c r="G15" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H15" t="s">
         <v>16</v>
@@ -5554,38 +5554,38 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>85</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C16" t="s">
         <v>30</v>
       </c>
       <c r="D16" t="s">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="E16" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F16" t="s">
         <v>14</v>
       </c>
       <c r="G16" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H16" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="I16" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>41</v>
+        <v>93</v>
       </c>
       <c r="B17" t="s">
         <v>34</v>
@@ -5597,24 +5597,24 @@
         <v>35</v>
       </c>
       <c r="E17" t="s">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="F17" t="s">
         <v>14</v>
       </c>
       <c r="G17" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H17" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="I17" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>52</v>
+        <v>87</v>
       </c>
       <c r="B18" t="s">
         <v>34</v>
@@ -5623,27 +5623,27 @@
         <v>30</v>
       </c>
       <c r="D18" t="s">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="E18" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="F18" t="s">
         <v>14</v>
       </c>
       <c r="G18" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H18" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="I18" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B19" t="s">
         <v>34</v>
@@ -5655,404 +5655,401 @@
         <v>35</v>
       </c>
       <c r="E19" t="s">
+        <v>109</v>
+      </c>
+      <c r="F19" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19" t="s">
+        <v>124</v>
+      </c>
+      <c r="H19" t="s">
+        <v>16</v>
+      </c>
+      <c r="I19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" t="s">
+        <v>14</v>
+      </c>
+      <c r="G20" t="s">
+        <v>124</v>
+      </c>
+      <c r="H20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I20" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>60</v>
+      </c>
+      <c r="B21" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E21" t="s">
+        <v>118</v>
+      </c>
+      <c r="F21" t="s">
+        <v>14</v>
+      </c>
+      <c r="G21" t="s">
+        <v>124</v>
+      </c>
+      <c r="H21" t="s">
+        <v>16</v>
+      </c>
+      <c r="I21" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>77</v>
+      </c>
+      <c r="B22" t="s">
+        <v>45</v>
+      </c>
+      <c r="C22" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" t="s">
+        <v>76</v>
+      </c>
+      <c r="E22" t="s">
+        <v>83</v>
+      </c>
+      <c r="F22" t="s">
+        <v>14</v>
+      </c>
+      <c r="G22" t="s">
+        <v>124</v>
+      </c>
+      <c r="H22" t="s">
+        <v>16</v>
+      </c>
+      <c r="I22" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>67</v>
+      </c>
+      <c r="B23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" t="s">
+        <v>68</v>
+      </c>
+      <c r="D23" t="s">
+        <v>35</v>
+      </c>
+      <c r="E23" t="s">
         <v>116</v>
       </c>
-      <c r="F19" t="s">
-        <v>14</v>
-      </c>
-      <c r="G19" t="s">
-        <v>125</v>
-      </c>
-      <c r="H19" t="s">
-        <v>16</v>
-      </c>
-      <c r="I19" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>60</v>
-      </c>
-      <c r="B20" t="s">
-        <v>45</v>
-      </c>
-      <c r="C20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D20" t="s">
-        <v>35</v>
-      </c>
-      <c r="E20" t="s">
+      <c r="F23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G23" t="s">
+        <v>124</v>
+      </c>
+      <c r="H23" t="s">
+        <v>16</v>
+      </c>
+      <c r="I23" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>79</v>
+      </c>
+      <c r="B24" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" t="s">
+        <v>30</v>
+      </c>
+      <c r="D24" t="s">
+        <v>76</v>
+      </c>
+      <c r="E24" t="s">
+        <v>114</v>
+      </c>
+      <c r="F24" t="s">
+        <v>14</v>
+      </c>
+      <c r="G24" t="s">
+        <v>124</v>
+      </c>
+      <c r="H24" t="s">
+        <v>16</v>
+      </c>
+      <c r="I24" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" t="s">
+        <v>30</v>
+      </c>
+      <c r="D25" t="s">
+        <v>12</v>
+      </c>
+      <c r="E25" t="s">
+        <v>115</v>
+      </c>
+      <c r="F25" t="s">
+        <v>14</v>
+      </c>
+      <c r="G25" t="s">
+        <v>124</v>
+      </c>
+      <c r="H25" t="s">
+        <v>16</v>
+      </c>
+      <c r="I25" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26" t="s">
+        <v>12</v>
+      </c>
+      <c r="E26" t="s">
+        <v>114</v>
+      </c>
+      <c r="F26" t="s">
+        <v>14</v>
+      </c>
+      <c r="G26" t="s">
+        <v>124</v>
+      </c>
+      <c r="H26" t="s">
+        <v>16</v>
+      </c>
+      <c r="I26" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>91</v>
+      </c>
+      <c r="B27" t="s">
+        <v>45</v>
+      </c>
+      <c r="C27" t="s">
+        <v>68</v>
+      </c>
+      <c r="D27" t="s">
+        <v>76</v>
+      </c>
+      <c r="E27" t="s">
+        <v>78</v>
+      </c>
+      <c r="F27" t="s">
+        <v>14</v>
+      </c>
+      <c r="G27" t="s">
+        <v>124</v>
+      </c>
+      <c r="H27" t="s">
+        <v>84</v>
+      </c>
+      <c r="I27" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>56</v>
+      </c>
+      <c r="B28" t="s">
+        <v>57</v>
+      </c>
+      <c r="C28" t="s">
+        <v>30</v>
+      </c>
+      <c r="D28" t="s">
+        <v>35</v>
+      </c>
+      <c r="E28" t="s">
+        <v>38</v>
+      </c>
+      <c r="F28" t="s">
+        <v>14</v>
+      </c>
+      <c r="G28" t="s">
+        <v>124</v>
+      </c>
+      <c r="H28" t="s">
+        <v>16</v>
+      </c>
+      <c r="I28" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>54</v>
+      </c>
+      <c r="B29" t="s">
+        <v>45</v>
+      </c>
+      <c r="C29" t="s">
+        <v>30</v>
+      </c>
+      <c r="D29" t="s">
+        <v>35</v>
+      </c>
+      <c r="E29" t="s">
+        <v>110</v>
+      </c>
+      <c r="F29" t="s">
+        <v>14</v>
+      </c>
+      <c r="G29" t="s">
+        <v>124</v>
+      </c>
+      <c r="H29" t="s">
+        <v>16</v>
+      </c>
+      <c r="I29" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>18</v>
+      </c>
+      <c r="B30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30" t="s">
+        <v>12</v>
+      </c>
+      <c r="E30" t="s">
+        <v>113</v>
+      </c>
+      <c r="F30" t="s">
+        <v>14</v>
+      </c>
+      <c r="G30" t="s">
+        <v>124</v>
+      </c>
+      <c r="H30" t="s">
+        <v>16</v>
+      </c>
+      <c r="I30" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>75</v>
+      </c>
+      <c r="B31" t="s">
+        <v>45</v>
+      </c>
+      <c r="C31" t="s">
+        <v>30</v>
+      </c>
+      <c r="D31" t="s">
+        <v>76</v>
+      </c>
+      <c r="E31" t="s">
         <v>119</v>
       </c>
-      <c r="F20" t="s">
-        <v>14</v>
-      </c>
-      <c r="G20" t="s">
-        <v>125</v>
-      </c>
-      <c r="H20" t="s">
-        <v>16</v>
-      </c>
-      <c r="I20" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>49</v>
-      </c>
-      <c r="B21" t="s">
-        <v>45</v>
-      </c>
-      <c r="C21" t="s">
-        <v>30</v>
-      </c>
-      <c r="D21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E21" t="s">
-        <v>119</v>
-      </c>
-      <c r="F21" t="s">
-        <v>14</v>
-      </c>
-      <c r="G21" t="s">
-        <v>125</v>
-      </c>
-      <c r="H21" t="s">
-        <v>16</v>
-      </c>
-      <c r="I21" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>54</v>
-      </c>
-      <c r="B22" t="s">
-        <v>45</v>
-      </c>
-      <c r="C22" t="s">
-        <v>30</v>
-      </c>
-      <c r="D22" t="s">
-        <v>35</v>
-      </c>
-      <c r="E22" t="s">
-        <v>111</v>
-      </c>
-      <c r="F22" t="s">
-        <v>14</v>
-      </c>
-      <c r="G22" t="s">
-        <v>125</v>
-      </c>
-      <c r="H22" t="s">
-        <v>16</v>
-      </c>
-      <c r="I22" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>65</v>
-      </c>
-      <c r="B23" t="s">
-        <v>45</v>
-      </c>
-      <c r="C23" t="s">
-        <v>30</v>
-      </c>
-      <c r="D23" t="s">
-        <v>35</v>
-      </c>
-      <c r="E23" t="s">
-        <v>83</v>
-      </c>
-      <c r="F23" t="s">
-        <v>14</v>
-      </c>
-      <c r="G23" t="s">
-        <v>125</v>
-      </c>
-      <c r="H23" t="s">
-        <v>16</v>
-      </c>
-      <c r="I23" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>56</v>
-      </c>
-      <c r="B24" t="s">
-        <v>57</v>
-      </c>
-      <c r="C24" t="s">
-        <v>30</v>
-      </c>
-      <c r="D24" t="s">
-        <v>35</v>
-      </c>
-      <c r="E24" t="s">
-        <v>38</v>
-      </c>
-      <c r="F24" t="s">
-        <v>14</v>
-      </c>
-      <c r="G24" t="s">
-        <v>125</v>
-      </c>
-      <c r="H24" t="s">
-        <v>16</v>
-      </c>
-      <c r="I24" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>58</v>
-      </c>
-      <c r="B25" t="s">
-        <v>45</v>
-      </c>
-      <c r="C25" t="s">
-        <v>30</v>
-      </c>
-      <c r="D25" t="s">
-        <v>35</v>
-      </c>
-      <c r="E25" t="s">
-        <v>40</v>
-      </c>
-      <c r="F25" t="s">
-        <v>14</v>
-      </c>
-      <c r="G25" t="s">
-        <v>125</v>
-      </c>
-      <c r="H25" t="s">
-        <v>16</v>
-      </c>
-      <c r="I25" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>63</v>
-      </c>
-      <c r="B26" t="s">
-        <v>45</v>
-      </c>
-      <c r="C26" t="s">
-        <v>30</v>
-      </c>
-      <c r="D26" t="s">
-        <v>35</v>
-      </c>
-      <c r="E26" t="s">
-        <v>40</v>
-      </c>
-      <c r="F26" t="s">
-        <v>14</v>
-      </c>
-      <c r="G26" t="s">
-        <v>125</v>
-      </c>
-      <c r="H26" t="s">
-        <v>16</v>
-      </c>
-      <c r="I26" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>61</v>
-      </c>
-      <c r="B27" t="s">
-        <v>45</v>
-      </c>
-      <c r="C27" t="s">
-        <v>30</v>
-      </c>
-      <c r="D27" t="s">
-        <v>35</v>
-      </c>
-      <c r="E27" t="s">
-        <v>69</v>
-      </c>
-      <c r="F27" t="s">
-        <v>14</v>
-      </c>
-      <c r="G27" t="s">
-        <v>125</v>
-      </c>
-      <c r="H27" t="s">
-        <v>16</v>
-      </c>
-      <c r="I27" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>44</v>
-      </c>
-      <c r="B28" t="s">
-        <v>45</v>
-      </c>
-      <c r="C28" t="s">
-        <v>30</v>
-      </c>
-      <c r="D28" t="s">
-        <v>35</v>
-      </c>
-      <c r="E28" t="s">
-        <v>78</v>
-      </c>
-      <c r="F28" t="s">
-        <v>14</v>
-      </c>
-      <c r="G28" t="s">
-        <v>125</v>
-      </c>
-      <c r="H28" t="s">
-        <v>16</v>
-      </c>
-      <c r="I28" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>67</v>
-      </c>
-      <c r="B29" t="s">
+      <c r="F31" t="s">
+        <v>14</v>
+      </c>
+      <c r="G31" t="s">
+        <v>124</v>
+      </c>
+      <c r="H31" t="s">
+        <v>16</v>
+      </c>
+      <c r="I31" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>20</v>
+      </c>
+      <c r="B32" t="s">
         <v>10</v>
       </c>
-      <c r="C29" t="s">
-        <v>68</v>
-      </c>
-      <c r="D29" t="s">
-        <v>35</v>
-      </c>
-      <c r="E29" t="s">
-        <v>117</v>
-      </c>
-      <c r="F29" t="s">
-        <v>14</v>
-      </c>
-      <c r="G29" t="s">
-        <v>125</v>
-      </c>
-      <c r="H29" t="s">
-        <v>16</v>
-      </c>
-      <c r="I29" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>72</v>
-      </c>
-      <c r="B30" t="s">
+      <c r="C32" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32" t="s">
+        <v>12</v>
+      </c>
+      <c r="E32" t="s">
+        <v>112</v>
+      </c>
+      <c r="F32" t="s">
+        <v>14</v>
+      </c>
+      <c r="G32" t="s">
+        <v>124</v>
+      </c>
+      <c r="H32" t="s">
+        <v>16</v>
+      </c>
+      <c r="I32" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>86</v>
+      </c>
+      <c r="B33" t="s">
         <v>34</v>
-      </c>
-      <c r="C30" t="s">
-        <v>68</v>
-      </c>
-      <c r="D30" t="s">
-        <v>35</v>
-      </c>
-      <c r="E30" t="s">
-        <v>110</v>
-      </c>
-      <c r="F30" t="s">
-        <v>14</v>
-      </c>
-      <c r="G30" t="s">
-        <v>125</v>
-      </c>
-      <c r="H30" t="s">
-        <v>16</v>
-      </c>
-      <c r="I30" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>70</v>
-      </c>
-      <c r="B31" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" t="s">
-        <v>68</v>
-      </c>
-      <c r="D31" t="s">
-        <v>35</v>
-      </c>
-      <c r="E31" t="s">
-        <v>116</v>
-      </c>
-      <c r="F31" t="s">
-        <v>14</v>
-      </c>
-      <c r="G31" t="s">
-        <v>125</v>
-      </c>
-      <c r="H31" t="s">
-        <v>16</v>
-      </c>
-      <c r="I31" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>74</v>
-      </c>
-      <c r="B32" t="s">
-        <v>34</v>
-      </c>
-      <c r="C32" t="s">
-        <v>68</v>
-      </c>
-      <c r="D32" t="s">
-        <v>35</v>
-      </c>
-      <c r="E32" t="s">
-        <v>15</v>
-      </c>
-      <c r="F32" t="s">
-        <v>14</v>
-      </c>
-      <c r="G32" t="s">
-        <v>125</v>
-      </c>
-      <c r="H32" t="s">
-        <v>16</v>
-      </c>
-      <c r="I32" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>79</v>
-      </c>
-      <c r="B33" t="s">
-        <v>45</v>
       </c>
       <c r="C33" t="s">
         <v>30</v>
@@ -6061,42 +6058,42 @@
         <v>76</v>
       </c>
       <c r="E33" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="F33" t="s">
         <v>14</v>
       </c>
       <c r="G33" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H33" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="I33" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>77</v>
+        <v>26</v>
       </c>
       <c r="B34" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="C34" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="D34" t="s">
-        <v>76</v>
+        <v>12</v>
       </c>
       <c r="E34" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="F34" t="s">
         <v>14</v>
       </c>
       <c r="G34" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H34" t="s">
         <v>16</v>
@@ -6105,9 +6102,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="B35" t="s">
         <v>45</v>
@@ -6116,16 +6113,16 @@
         <v>30</v>
       </c>
       <c r="D35" t="s">
-        <v>76</v>
+        <v>35</v>
       </c>
       <c r="E35" t="s">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="F35" t="s">
         <v>14</v>
       </c>
       <c r="G35" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H35" t="s">
         <v>16</v>
@@ -6134,27 +6131,27 @@
         <v>17</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>80</v>
+        <v>21</v>
       </c>
       <c r="B36" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="C36" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="D36" t="s">
-        <v>76</v>
+        <v>12</v>
       </c>
       <c r="E36" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F36" t="s">
         <v>14</v>
       </c>
       <c r="G36" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H36" t="s">
         <v>16</v>
@@ -6163,27 +6160,27 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="B37" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C37" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="D37" t="s">
-        <v>76</v>
+        <v>35</v>
       </c>
       <c r="E37" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F37" t="s">
         <v>14</v>
       </c>
       <c r="G37" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H37" t="s">
         <v>16</v>
@@ -6192,38 +6189,38 @@
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>87</v>
+        <v>9</v>
       </c>
       <c r="B38" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="C38" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="D38" t="s">
-        <v>76</v>
+        <v>12</v>
       </c>
       <c r="E38" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="F38" t="s">
         <v>14</v>
       </c>
       <c r="G38" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H38" t="s">
-        <v>84</v>
+        <v>16</v>
       </c>
       <c r="I38" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="B39" t="s">
         <v>34</v>
@@ -6232,27 +6229,27 @@
         <v>30</v>
       </c>
       <c r="D39" t="s">
-        <v>76</v>
+        <v>35</v>
       </c>
       <c r="E39" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="F39" t="s">
         <v>14</v>
       </c>
       <c r="G39" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H39" t="s">
-        <v>84</v>
+        <v>16</v>
       </c>
       <c r="I39" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>82</v>
+        <v>44</v>
       </c>
       <c r="B40" t="s">
         <v>45</v>
@@ -6261,175 +6258,175 @@
         <v>30</v>
       </c>
       <c r="D40" t="s">
-        <v>76</v>
+        <v>35</v>
       </c>
       <c r="E40" t="s">
-        <v>122</v>
+        <v>78</v>
       </c>
       <c r="F40" t="s">
         <v>14</v>
       </c>
       <c r="G40" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H40" t="s">
-        <v>84</v>
+        <v>16</v>
       </c>
       <c r="I40" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>85</v>
+        <v>32</v>
       </c>
       <c r="B41" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="C41" t="s">
         <v>30</v>
       </c>
       <c r="D41" t="s">
-        <v>76</v>
+        <v>12</v>
       </c>
       <c r="E41" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F41" t="s">
         <v>14</v>
       </c>
       <c r="G41" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H41" t="s">
-        <v>84</v>
+        <v>16</v>
       </c>
       <c r="I41" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>88</v>
+        <v>33</v>
       </c>
       <c r="B42" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C42" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="D42" t="s">
-        <v>76</v>
+        <v>35</v>
       </c>
       <c r="E42" t="s">
-        <v>118</v>
+        <v>40</v>
       </c>
       <c r="F42" t="s">
         <v>14</v>
       </c>
       <c r="G42" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H42" t="s">
-        <v>84</v>
+        <v>16</v>
       </c>
       <c r="I42" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="B43" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C43" t="s">
         <v>68</v>
       </c>
       <c r="D43" t="s">
-        <v>76</v>
+        <v>35</v>
       </c>
       <c r="E43" t="s">
-        <v>118</v>
+        <v>15</v>
       </c>
       <c r="F43" t="s">
         <v>14</v>
       </c>
       <c r="G43" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H43" t="s">
-        <v>84</v>
+        <v>16</v>
       </c>
       <c r="I43" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="B44" t="s">
         <v>45</v>
       </c>
       <c r="C44" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="D44" t="s">
-        <v>76</v>
+        <v>35</v>
       </c>
       <c r="E44" t="s">
-        <v>122</v>
+        <v>83</v>
       </c>
       <c r="F44" t="s">
         <v>14</v>
       </c>
       <c r="G44" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H44" t="s">
-        <v>84</v>
+        <v>16</v>
       </c>
       <c r="I44" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>91</v>
+        <v>37</v>
       </c>
       <c r="B45" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C45" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="D45" t="s">
-        <v>76</v>
+        <v>35</v>
       </c>
       <c r="E45" t="s">
-        <v>78</v>
+        <v>112</v>
       </c>
       <c r="F45" t="s">
         <v>14</v>
       </c>
       <c r="G45" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H45" t="s">
-        <v>84</v>
+        <v>16</v>
       </c>
       <c r="I45" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>93</v>
+        <v>61</v>
       </c>
       <c r="B46" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C46" t="s">
         <v>30</v>
@@ -6438,24 +6435,24 @@
         <v>35</v>
       </c>
       <c r="E46" t="s">
-        <v>123</v>
+        <v>69</v>
       </c>
       <c r="F46" t="s">
         <v>14</v>
       </c>
       <c r="G46" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H46" t="s">
-        <v>84</v>
+        <v>16</v>
       </c>
       <c r="I46" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>94</v>
+        <v>41</v>
       </c>
       <c r="B47" t="s">
         <v>34</v>
@@ -6467,27 +6464,27 @@
         <v>35</v>
       </c>
       <c r="E47" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="F47" t="s">
         <v>14</v>
       </c>
       <c r="G47" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H47" t="s">
-        <v>84</v>
+        <v>16</v>
       </c>
       <c r="I47" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>92</v>
+        <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C48" t="s">
         <v>30</v>
@@ -6496,27 +6493,27 @@
         <v>35</v>
       </c>
       <c r="E48" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F48" t="s">
         <v>14</v>
       </c>
       <c r="G48" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H48" t="s">
-        <v>84</v>
+        <v>16</v>
       </c>
       <c r="I48" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="B49" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="C49" t="s">
         <v>68</v>
@@ -6525,25 +6522,28 @@
         <v>35</v>
       </c>
       <c r="E49" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="F49" t="s">
         <v>14</v>
       </c>
       <c r="G49" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H49" t="s">
-        <v>84</v>
+        <v>16</v>
       </c>
       <c r="I49" t="s">
         <v>17</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I49">
+    <sortCondition ref="A2:A49"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:F7 H1:I49 A9:F49 A8:D8 F8" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:F1 H1:I1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>